--- a/site/exports/hnu-literature.xlsx
+++ b/site/exports/hnu-literature.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,10 +569,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>文学院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Bachelor education not stated in accepted profile.；Master award and end date unknown.；Separate doctoral award date unknown; graduation month is not silently substituted.；Formal dissertation advisers not established.；Two disclosed postdoctoral periods overlap; no inferred exclusivity or resolution.；Publication years, publishers and precise authorship roles for selected books not disclosed.；Real-time current employment and organization legal hierarchy not verified.；来源记载职业信息：系室：语言学与应用语言学教研室。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。；来源记载职业信息：来源单位名称：中国语言文学学院。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,12 +638,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18.2" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="29.4" customWidth="1" min="2" max="2"/>
+    <col width="16.8" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -666,7 +720,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -951,13 +1005,437 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>硕士学位</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>湖南师范大学</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Master study began in 2000; end date and award not stated.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>文学博士学位</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>上海师范大学</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2003-09</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2006-06</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>June 2006 is explicitly the graduation month. An award is explicit, but its separate date is not; award_date remains null.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源unit：语言研究所</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral_research</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>香港科技大学</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2007-09</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Postdoctoral research, not another degree. Overlaps the next disclosed postdoctoral start; no correction or inferred exclusivity.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源unit：中国语言中心博士后工作站</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral_research</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>湖南师范大学</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2008-12</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Only start month stated; no end inferred.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源unit：博士后流动站</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2006-09</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>“同年” resolves to 2006 from the immediately preceding doctoral graduation sentence. The source says 至今; no real-time employment confirmation or end date inferred.；任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（单位）：文学院</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>教授，副院长，博士生导师</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Profile-listed roles only, no real-time status confirmation.；任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（单位）：中国语言文学学院</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>首任汉语教师</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>美国科罗拉多州立大学</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2014-09</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Employment/teaching appointment, not visiting study or degree.；任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（单位）：孔子学院</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S5"/>
+  <autoFilter ref="A1:S12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -969,14 +1447,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="50.4" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
@@ -1148,11 +1626,215 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>鲍厚星</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>stage_specific_mentorship</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>硕士阶段</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>师从；来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>潘悟云</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>stage_specific_mentorship</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>博士阶段</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>师从；来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>朱晓农</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>stage_specific_mentorship</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>博士后阶段</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>师从；来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>蒋冀骋</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>stage_specific_mentorship</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>博士后阶段</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>师从；来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1164,7 +1846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1355,8 +2037,108 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>湖南通道本地话</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>湖南方言实验语音学研究</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1364,6 +2146,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1375,14 +2161,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="25.2" customWidth="1" min="2" max="2"/>
+    <col width="64.39999999999999" customWidth="1" min="2" max="2"/>
     <col width="57.4" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="33.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1490,11 +2276,87 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-hnu-pengjianguo-s001-4f4aade66a9a</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/info/1013/4406.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:21:47.758Z</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>彭建国</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-hnu-pengjianguo-s002-bde42687be00</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://wxy.hnu.edu.cn/szdw/jslb2.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:21:39.668Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>hnu</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>湖南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
